--- a/data/degradation/task_spectrum_30day_example.xlsx
+++ b/data/degradation/task_spectrum_30day_example.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O331"/>
+  <dimension ref="A1:P331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,11 @@
           <t>oil_temperature_c</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>seconds_per_degree</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -542,6 +547,7 @@
       <c r="O2" t="n">
         <v>35</v>
       </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -591,6 +597,7 @@
       <c r="O3" t="n">
         <v>40</v>
       </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,6 +647,7 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -689,6 +697,7 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -738,6 +747,7 @@
       <c r="O6" t="n">
         <v>50</v>
       </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -787,6 +797,7 @@
       <c r="O7" t="n">
         <v>55</v>
       </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -836,6 +847,7 @@
       <c r="O8" t="n">
         <v>55</v>
       </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -885,6 +897,7 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -934,6 +947,7 @@
       <c r="O10" t="n">
         <v>50</v>
       </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -983,6 +997,7 @@
       <c r="O11" t="n">
         <v>50</v>
       </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1032,6 +1047,7 @@
       <c r="O12" t="n">
         <v>45</v>
       </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1081,6 +1097,7 @@
       <c r="O13" t="n">
         <v>35</v>
       </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1130,6 +1147,7 @@
       <c r="O14" t="n">
         <v>40</v>
       </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1179,6 +1197,7 @@
       <c r="O15" t="n">
         <v>45</v>
       </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1228,6 +1247,7 @@
       <c r="O16" t="n">
         <v>45</v>
       </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1277,6 +1297,7 @@
       <c r="O17" t="n">
         <v>50</v>
       </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1326,6 +1347,7 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1375,6 +1397,7 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1424,6 +1447,7 @@
       <c r="O20" t="n">
         <v>55</v>
       </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1473,6 +1497,7 @@
       <c r="O21" t="n">
         <v>50</v>
       </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1522,6 +1547,7 @@
       <c r="O22" t="n">
         <v>50</v>
       </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1571,6 +1597,7 @@
       <c r="O23" t="n">
         <v>45</v>
       </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1620,6 +1647,7 @@
       <c r="O24" t="n">
         <v>35</v>
       </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1669,6 +1697,7 @@
       <c r="O25" t="n">
         <v>40</v>
       </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1718,6 +1747,7 @@
       <c r="O26" t="n">
         <v>45</v>
       </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1767,6 +1797,7 @@
       <c r="O27" t="n">
         <v>45</v>
       </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1816,6 +1847,7 @@
       <c r="O28" t="n">
         <v>50</v>
       </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1865,6 +1897,7 @@
       <c r="O29" t="n">
         <v>55</v>
       </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1914,6 +1947,7 @@
       <c r="O30" t="n">
         <v>55</v>
       </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1963,6 +1997,7 @@
       <c r="O31" t="n">
         <v>55</v>
       </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2012,6 +2047,7 @@
       <c r="O32" t="n">
         <v>50</v>
       </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2061,6 +2097,7 @@
       <c r="O33" t="n">
         <v>50</v>
       </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2110,6 +2147,7 @@
       <c r="O34" t="n">
         <v>45</v>
       </c>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2159,6 +2197,7 @@
       <c r="O35" t="n">
         <v>35</v>
       </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2208,6 +2247,7 @@
       <c r="O36" t="n">
         <v>40</v>
       </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2257,6 +2297,7 @@
       <c r="O37" t="n">
         <v>45</v>
       </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2306,6 +2347,7 @@
       <c r="O38" t="n">
         <v>45</v>
       </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2355,6 +2397,7 @@
       <c r="O39" t="n">
         <v>50</v>
       </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2404,6 +2447,7 @@
       <c r="O40" t="n">
         <v>55</v>
       </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2453,6 +2497,7 @@
       <c r="O41" t="n">
         <v>55</v>
       </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2502,6 +2547,7 @@
       <c r="O42" t="n">
         <v>55</v>
       </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2551,6 +2597,7 @@
       <c r="O43" t="n">
         <v>50</v>
       </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2600,6 +2647,7 @@
       <c r="O44" t="n">
         <v>50</v>
       </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2649,6 +2697,7 @@
       <c r="O45" t="n">
         <v>45</v>
       </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2698,6 +2747,7 @@
       <c r="O46" t="n">
         <v>35</v>
       </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2747,6 +2797,7 @@
       <c r="O47" t="n">
         <v>40</v>
       </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2796,6 +2847,7 @@
       <c r="O48" t="n">
         <v>45</v>
       </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2845,6 +2897,7 @@
       <c r="O49" t="n">
         <v>45</v>
       </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2894,6 +2947,7 @@
       <c r="O50" t="n">
         <v>50</v>
       </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2943,6 +2997,7 @@
       <c r="O51" t="n">
         <v>55</v>
       </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2992,6 +3047,7 @@
       <c r="O52" t="n">
         <v>55</v>
       </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3041,6 +3097,7 @@
       <c r="O53" t="n">
         <v>55</v>
       </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3090,6 +3147,7 @@
       <c r="O54" t="n">
         <v>50</v>
       </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3139,6 +3197,7 @@
       <c r="O55" t="n">
         <v>50</v>
       </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3188,6 +3247,7 @@
       <c r="O56" t="n">
         <v>45</v>
       </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3237,6 +3297,7 @@
       <c r="O57" t="n">
         <v>35</v>
       </c>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3286,6 +3347,7 @@
       <c r="O58" t="n">
         <v>40</v>
       </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3335,6 +3397,7 @@
       <c r="O59" t="n">
         <v>45</v>
       </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3384,6 +3447,7 @@
       <c r="O60" t="n">
         <v>45</v>
       </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3433,6 +3497,7 @@
       <c r="O61" t="n">
         <v>50</v>
       </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3482,6 +3547,7 @@
       <c r="O62" t="n">
         <v>55</v>
       </c>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3531,6 +3597,7 @@
       <c r="O63" t="n">
         <v>55</v>
       </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3580,6 +3647,7 @@
       <c r="O64" t="n">
         <v>55</v>
       </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3629,6 +3697,7 @@
       <c r="O65" t="n">
         <v>50</v>
       </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3678,6 +3747,7 @@
       <c r="O66" t="n">
         <v>50</v>
       </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3727,6 +3797,7 @@
       <c r="O67" t="n">
         <v>45</v>
       </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3776,6 +3847,7 @@
       <c r="O68" t="n">
         <v>35</v>
       </c>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3825,6 +3897,7 @@
       <c r="O69" t="n">
         <v>40</v>
       </c>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3874,6 +3947,7 @@
       <c r="O70" t="n">
         <v>45</v>
       </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3923,6 +3997,7 @@
       <c r="O71" t="n">
         <v>45</v>
       </c>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3972,6 +4047,7 @@
       <c r="O72" t="n">
         <v>50</v>
       </c>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4021,6 +4097,7 @@
       <c r="O73" t="n">
         <v>55</v>
       </c>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4070,6 +4147,7 @@
       <c r="O74" t="n">
         <v>55</v>
       </c>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4119,6 +4197,7 @@
       <c r="O75" t="n">
         <v>55</v>
       </c>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4168,6 +4247,7 @@
       <c r="O76" t="n">
         <v>50</v>
       </c>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4217,6 +4297,7 @@
       <c r="O77" t="n">
         <v>50</v>
       </c>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4266,6 +4347,7 @@
       <c r="O78" t="n">
         <v>45</v>
       </c>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4315,6 +4397,7 @@
       <c r="O79" t="n">
         <v>35</v>
       </c>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4364,6 +4447,7 @@
       <c r="O80" t="n">
         <v>40</v>
       </c>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4413,6 +4497,7 @@
       <c r="O81" t="n">
         <v>45</v>
       </c>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4462,6 +4547,7 @@
       <c r="O82" t="n">
         <v>45</v>
       </c>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4511,6 +4597,7 @@
       <c r="O83" t="n">
         <v>50</v>
       </c>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4560,6 +4647,7 @@
       <c r="O84" t="n">
         <v>55</v>
       </c>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4609,6 +4697,7 @@
       <c r="O85" t="n">
         <v>55</v>
       </c>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4658,6 +4747,7 @@
       <c r="O86" t="n">
         <v>55</v>
       </c>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4707,6 +4797,7 @@
       <c r="O87" t="n">
         <v>50</v>
       </c>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4756,6 +4847,7 @@
       <c r="O88" t="n">
         <v>50</v>
       </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4805,6 +4897,7 @@
       <c r="O89" t="n">
         <v>45</v>
       </c>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4854,6 +4947,7 @@
       <c r="O90" t="n">
         <v>35</v>
       </c>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4903,6 +4997,7 @@
       <c r="O91" t="n">
         <v>40</v>
       </c>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4952,6 +5047,7 @@
       <c r="O92" t="n">
         <v>45</v>
       </c>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5001,6 +5097,7 @@
       <c r="O93" t="n">
         <v>45</v>
       </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5050,6 +5147,7 @@
       <c r="O94" t="n">
         <v>50</v>
       </c>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5099,6 +5197,7 @@
       <c r="O95" t="n">
         <v>55</v>
       </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5148,6 +5247,7 @@
       <c r="O96" t="n">
         <v>55</v>
       </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5197,6 +5297,7 @@
       <c r="O97" t="n">
         <v>55</v>
       </c>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5246,6 +5347,7 @@
       <c r="O98" t="n">
         <v>50</v>
       </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5295,6 +5397,7 @@
       <c r="O99" t="n">
         <v>50</v>
       </c>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5344,6 +5447,7 @@
       <c r="O100" t="n">
         <v>45</v>
       </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5393,6 +5497,7 @@
       <c r="O101" t="n">
         <v>35</v>
       </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5442,6 +5547,7 @@
       <c r="O102" t="n">
         <v>40</v>
       </c>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5491,6 +5597,7 @@
       <c r="O103" t="n">
         <v>45</v>
       </c>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5540,6 +5647,7 @@
       <c r="O104" t="n">
         <v>45</v>
       </c>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5589,6 +5697,7 @@
       <c r="O105" t="n">
         <v>50</v>
       </c>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5638,6 +5747,7 @@
       <c r="O106" t="n">
         <v>55</v>
       </c>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5687,6 +5797,7 @@
       <c r="O107" t="n">
         <v>55</v>
       </c>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5736,6 +5847,7 @@
       <c r="O108" t="n">
         <v>55</v>
       </c>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5785,6 +5897,7 @@
       <c r="O109" t="n">
         <v>50</v>
       </c>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5834,6 +5947,7 @@
       <c r="O110" t="n">
         <v>50</v>
       </c>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5883,6 +5997,7 @@
       <c r="O111" t="n">
         <v>45</v>
       </c>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5932,6 +6047,7 @@
       <c r="O112" t="n">
         <v>35</v>
       </c>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5981,6 +6097,7 @@
       <c r="O113" t="n">
         <v>40</v>
       </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6030,6 +6147,7 @@
       <c r="O114" t="n">
         <v>45</v>
       </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6079,6 +6197,7 @@
       <c r="O115" t="n">
         <v>45</v>
       </c>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6128,6 +6247,7 @@
       <c r="O116" t="n">
         <v>50</v>
       </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6177,6 +6297,7 @@
       <c r="O117" t="n">
         <v>55</v>
       </c>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6226,6 +6347,7 @@
       <c r="O118" t="n">
         <v>55</v>
       </c>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6275,6 +6397,7 @@
       <c r="O119" t="n">
         <v>55</v>
       </c>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6324,6 +6447,7 @@
       <c r="O120" t="n">
         <v>50</v>
       </c>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6373,6 +6497,7 @@
       <c r="O121" t="n">
         <v>50</v>
       </c>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6422,6 +6547,7 @@
       <c r="O122" t="n">
         <v>45</v>
       </c>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6471,6 +6597,7 @@
       <c r="O123" t="n">
         <v>35</v>
       </c>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6520,6 +6647,7 @@
       <c r="O124" t="n">
         <v>40</v>
       </c>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6569,6 +6697,7 @@
       <c r="O125" t="n">
         <v>45</v>
       </c>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6618,6 +6747,7 @@
       <c r="O126" t="n">
         <v>45</v>
       </c>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6667,6 +6797,7 @@
       <c r="O127" t="n">
         <v>50</v>
       </c>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6716,6 +6847,7 @@
       <c r="O128" t="n">
         <v>55</v>
       </c>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6765,6 +6897,7 @@
       <c r="O129" t="n">
         <v>55</v>
       </c>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6814,6 +6947,7 @@
       <c r="O130" t="n">
         <v>55</v>
       </c>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6863,6 +6997,7 @@
       <c r="O131" t="n">
         <v>50</v>
       </c>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6912,6 +7047,7 @@
       <c r="O132" t="n">
         <v>50</v>
       </c>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6961,6 +7097,7 @@
       <c r="O133" t="n">
         <v>45</v>
       </c>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7010,6 +7147,7 @@
       <c r="O134" t="n">
         <v>35</v>
       </c>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7059,6 +7197,7 @@
       <c r="O135" t="n">
         <v>40</v>
       </c>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7108,6 +7247,7 @@
       <c r="O136" t="n">
         <v>45</v>
       </c>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7157,6 +7297,7 @@
       <c r="O137" t="n">
         <v>45</v>
       </c>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7206,6 +7347,7 @@
       <c r="O138" t="n">
         <v>50</v>
       </c>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7255,6 +7397,7 @@
       <c r="O139" t="n">
         <v>55</v>
       </c>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7304,6 +7447,7 @@
       <c r="O140" t="n">
         <v>55</v>
       </c>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7353,6 +7497,7 @@
       <c r="O141" t="n">
         <v>55</v>
       </c>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7402,6 +7547,7 @@
       <c r="O142" t="n">
         <v>50</v>
       </c>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7451,6 +7597,7 @@
       <c r="O143" t="n">
         <v>50</v>
       </c>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7500,6 +7647,7 @@
       <c r="O144" t="n">
         <v>45</v>
       </c>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7549,6 +7697,7 @@
       <c r="O145" t="n">
         <v>35</v>
       </c>
+      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7598,6 +7747,7 @@
       <c r="O146" t="n">
         <v>40</v>
       </c>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7647,6 +7797,7 @@
       <c r="O147" t="n">
         <v>45</v>
       </c>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7696,6 +7847,7 @@
       <c r="O148" t="n">
         <v>45</v>
       </c>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7745,6 +7897,7 @@
       <c r="O149" t="n">
         <v>50</v>
       </c>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7794,6 +7947,7 @@
       <c r="O150" t="n">
         <v>55</v>
       </c>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7843,6 +7997,7 @@
       <c r="O151" t="n">
         <v>55</v>
       </c>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7892,6 +8047,7 @@
       <c r="O152" t="n">
         <v>55</v>
       </c>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7941,6 +8097,7 @@
       <c r="O153" t="n">
         <v>50</v>
       </c>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7990,6 +8147,7 @@
       <c r="O154" t="n">
         <v>50</v>
       </c>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8039,6 +8197,7 @@
       <c r="O155" t="n">
         <v>45</v>
       </c>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8088,6 +8247,7 @@
       <c r="O156" t="n">
         <v>35</v>
       </c>
+      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8137,6 +8297,7 @@
       <c r="O157" t="n">
         <v>40</v>
       </c>
+      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8186,6 +8347,7 @@
       <c r="O158" t="n">
         <v>45</v>
       </c>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8235,6 +8397,7 @@
       <c r="O159" t="n">
         <v>45</v>
       </c>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8284,6 +8447,7 @@
       <c r="O160" t="n">
         <v>50</v>
       </c>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8333,6 +8497,7 @@
       <c r="O161" t="n">
         <v>55</v>
       </c>
+      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8382,6 +8547,7 @@
       <c r="O162" t="n">
         <v>55</v>
       </c>
+      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8431,6 +8597,7 @@
       <c r="O163" t="n">
         <v>55</v>
       </c>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8480,6 +8647,7 @@
       <c r="O164" t="n">
         <v>50</v>
       </c>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8529,6 +8697,7 @@
       <c r="O165" t="n">
         <v>50</v>
       </c>
+      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8578,6 +8747,7 @@
       <c r="O166" t="n">
         <v>45</v>
       </c>
+      <c r="P166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8627,6 +8797,7 @@
       <c r="O167" t="n">
         <v>35</v>
       </c>
+      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8676,6 +8847,7 @@
       <c r="O168" t="n">
         <v>40</v>
       </c>
+      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8725,6 +8897,7 @@
       <c r="O169" t="n">
         <v>45</v>
       </c>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8774,6 +8947,7 @@
       <c r="O170" t="n">
         <v>45</v>
       </c>
+      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8823,6 +8997,7 @@
       <c r="O171" t="n">
         <v>50</v>
       </c>
+      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8872,6 +9047,7 @@
       <c r="O172" t="n">
         <v>55</v>
       </c>
+      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8921,6 +9097,7 @@
       <c r="O173" t="n">
         <v>55</v>
       </c>
+      <c r="P173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8970,6 +9147,7 @@
       <c r="O174" t="n">
         <v>55</v>
       </c>
+      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9019,6 +9197,7 @@
       <c r="O175" t="n">
         <v>50</v>
       </c>
+      <c r="P175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9068,6 +9247,7 @@
       <c r="O176" t="n">
         <v>50</v>
       </c>
+      <c r="P176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9117,6 +9297,7 @@
       <c r="O177" t="n">
         <v>45</v>
       </c>
+      <c r="P177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9166,6 +9347,7 @@
       <c r="O178" t="n">
         <v>35</v>
       </c>
+      <c r="P178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9215,6 +9397,7 @@
       <c r="O179" t="n">
         <v>40</v>
       </c>
+      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9264,6 +9447,7 @@
       <c r="O180" t="n">
         <v>45</v>
       </c>
+      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9313,6 +9497,7 @@
       <c r="O181" t="n">
         <v>45</v>
       </c>
+      <c r="P181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9362,6 +9547,7 @@
       <c r="O182" t="n">
         <v>50</v>
       </c>
+      <c r="P182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9411,6 +9597,7 @@
       <c r="O183" t="n">
         <v>55</v>
       </c>
+      <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9460,6 +9647,7 @@
       <c r="O184" t="n">
         <v>55</v>
       </c>
+      <c r="P184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9509,6 +9697,7 @@
       <c r="O185" t="n">
         <v>55</v>
       </c>
+      <c r="P185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9558,6 +9747,7 @@
       <c r="O186" t="n">
         <v>50</v>
       </c>
+      <c r="P186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9607,6 +9797,7 @@
       <c r="O187" t="n">
         <v>50</v>
       </c>
+      <c r="P187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9656,6 +9847,7 @@
       <c r="O188" t="n">
         <v>45</v>
       </c>
+      <c r="P188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9705,6 +9897,7 @@
       <c r="O189" t="n">
         <v>35</v>
       </c>
+      <c r="P189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9754,6 +9947,7 @@
       <c r="O190" t="n">
         <v>40</v>
       </c>
+      <c r="P190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9803,6 +9997,7 @@
       <c r="O191" t="n">
         <v>45</v>
       </c>
+      <c r="P191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9852,6 +10047,7 @@
       <c r="O192" t="n">
         <v>45</v>
       </c>
+      <c r="P192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9901,6 +10097,7 @@
       <c r="O193" t="n">
         <v>50</v>
       </c>
+      <c r="P193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9950,6 +10147,7 @@
       <c r="O194" t="n">
         <v>55</v>
       </c>
+      <c r="P194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9999,6 +10197,7 @@
       <c r="O195" t="n">
         <v>55</v>
       </c>
+      <c r="P195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10048,6 +10247,7 @@
       <c r="O196" t="n">
         <v>55</v>
       </c>
+      <c r="P196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10097,6 +10297,7 @@
       <c r="O197" t="n">
         <v>50</v>
       </c>
+      <c r="P197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10146,6 +10347,7 @@
       <c r="O198" t="n">
         <v>50</v>
       </c>
+      <c r="P198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10195,6 +10397,7 @@
       <c r="O199" t="n">
         <v>45</v>
       </c>
+      <c r="P199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10244,6 +10447,7 @@
       <c r="O200" t="n">
         <v>35</v>
       </c>
+      <c r="P200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10293,6 +10497,7 @@
       <c r="O201" t="n">
         <v>40</v>
       </c>
+      <c r="P201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10342,6 +10547,7 @@
       <c r="O202" t="n">
         <v>45</v>
       </c>
+      <c r="P202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10391,6 +10597,7 @@
       <c r="O203" t="n">
         <v>45</v>
       </c>
+      <c r="P203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10440,6 +10647,7 @@
       <c r="O204" t="n">
         <v>50</v>
       </c>
+      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10489,6 +10697,7 @@
       <c r="O205" t="n">
         <v>55</v>
       </c>
+      <c r="P205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10538,6 +10747,7 @@
       <c r="O206" t="n">
         <v>55</v>
       </c>
+      <c r="P206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10587,6 +10797,7 @@
       <c r="O207" t="n">
         <v>55</v>
       </c>
+      <c r="P207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10636,6 +10847,7 @@
       <c r="O208" t="n">
         <v>50</v>
       </c>
+      <c r="P208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10685,6 +10897,7 @@
       <c r="O209" t="n">
         <v>50</v>
       </c>
+      <c r="P209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10734,6 +10947,7 @@
       <c r="O210" t="n">
         <v>45</v>
       </c>
+      <c r="P210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10783,6 +10997,7 @@
       <c r="O211" t="n">
         <v>35</v>
       </c>
+      <c r="P211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10832,6 +11047,7 @@
       <c r="O212" t="n">
         <v>40</v>
       </c>
+      <c r="P212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10881,6 +11097,7 @@
       <c r="O213" t="n">
         <v>45</v>
       </c>
+      <c r="P213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10930,6 +11147,7 @@
       <c r="O214" t="n">
         <v>45</v>
       </c>
+      <c r="P214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10979,6 +11197,7 @@
       <c r="O215" t="n">
         <v>50</v>
       </c>
+      <c r="P215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11028,6 +11247,7 @@
       <c r="O216" t="n">
         <v>55</v>
       </c>
+      <c r="P216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11077,6 +11297,7 @@
       <c r="O217" t="n">
         <v>55</v>
       </c>
+      <c r="P217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11126,6 +11347,7 @@
       <c r="O218" t="n">
         <v>55</v>
       </c>
+      <c r="P218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11175,6 +11397,7 @@
       <c r="O219" t="n">
         <v>50</v>
       </c>
+      <c r="P219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11224,6 +11447,7 @@
       <c r="O220" t="n">
         <v>50</v>
       </c>
+      <c r="P220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11273,6 +11497,7 @@
       <c r="O221" t="n">
         <v>45</v>
       </c>
+      <c r="P221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11322,6 +11547,7 @@
       <c r="O222" t="n">
         <v>35</v>
       </c>
+      <c r="P222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11371,6 +11597,7 @@
       <c r="O223" t="n">
         <v>40</v>
       </c>
+      <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11420,6 +11647,7 @@
       <c r="O224" t="n">
         <v>45</v>
       </c>
+      <c r="P224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11469,6 +11697,7 @@
       <c r="O225" t="n">
         <v>45</v>
       </c>
+      <c r="P225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11518,6 +11747,7 @@
       <c r="O226" t="n">
         <v>50</v>
       </c>
+      <c r="P226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11567,6 +11797,7 @@
       <c r="O227" t="n">
         <v>55</v>
       </c>
+      <c r="P227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11616,6 +11847,7 @@
       <c r="O228" t="n">
         <v>55</v>
       </c>
+      <c r="P228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11665,6 +11897,7 @@
       <c r="O229" t="n">
         <v>55</v>
       </c>
+      <c r="P229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11714,6 +11947,7 @@
       <c r="O230" t="n">
         <v>50</v>
       </c>
+      <c r="P230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11763,6 +11997,7 @@
       <c r="O231" t="n">
         <v>50</v>
       </c>
+      <c r="P231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11812,6 +12047,7 @@
       <c r="O232" t="n">
         <v>45</v>
       </c>
+      <c r="P232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11861,6 +12097,7 @@
       <c r="O233" t="n">
         <v>35</v>
       </c>
+      <c r="P233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11910,6 +12147,7 @@
       <c r="O234" t="n">
         <v>40</v>
       </c>
+      <c r="P234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11959,6 +12197,7 @@
       <c r="O235" t="n">
         <v>45</v>
       </c>
+      <c r="P235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12008,6 +12247,7 @@
       <c r="O236" t="n">
         <v>45</v>
       </c>
+      <c r="P236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12057,6 +12297,7 @@
       <c r="O237" t="n">
         <v>50</v>
       </c>
+      <c r="P237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12106,6 +12347,7 @@
       <c r="O238" t="n">
         <v>55</v>
       </c>
+      <c r="P238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12155,6 +12397,7 @@
       <c r="O239" t="n">
         <v>55</v>
       </c>
+      <c r="P239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12204,6 +12447,7 @@
       <c r="O240" t="n">
         <v>55</v>
       </c>
+      <c r="P240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12253,6 +12497,7 @@
       <c r="O241" t="n">
         <v>50</v>
       </c>
+      <c r="P241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12302,6 +12547,7 @@
       <c r="O242" t="n">
         <v>50</v>
       </c>
+      <c r="P242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12351,6 +12597,7 @@
       <c r="O243" t="n">
         <v>45</v>
       </c>
+      <c r="P243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12400,6 +12647,7 @@
       <c r="O244" t="n">
         <v>35</v>
       </c>
+      <c r="P244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12449,6 +12697,7 @@
       <c r="O245" t="n">
         <v>40</v>
       </c>
+      <c r="P245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12498,6 +12747,7 @@
       <c r="O246" t="n">
         <v>45</v>
       </c>
+      <c r="P246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12547,6 +12797,7 @@
       <c r="O247" t="n">
         <v>45</v>
       </c>
+      <c r="P247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12596,6 +12847,7 @@
       <c r="O248" t="n">
         <v>50</v>
       </c>
+      <c r="P248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12645,6 +12897,7 @@
       <c r="O249" t="n">
         <v>55</v>
       </c>
+      <c r="P249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12694,6 +12947,7 @@
       <c r="O250" t="n">
         <v>55</v>
       </c>
+      <c r="P250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12743,6 +12997,7 @@
       <c r="O251" t="n">
         <v>55</v>
       </c>
+      <c r="P251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12792,6 +13047,7 @@
       <c r="O252" t="n">
         <v>50</v>
       </c>
+      <c r="P252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12841,6 +13097,7 @@
       <c r="O253" t="n">
         <v>50</v>
       </c>
+      <c r="P253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12890,6 +13147,7 @@
       <c r="O254" t="n">
         <v>45</v>
       </c>
+      <c r="P254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12939,6 +13197,7 @@
       <c r="O255" t="n">
         <v>35</v>
       </c>
+      <c r="P255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12988,6 +13247,7 @@
       <c r="O256" t="n">
         <v>40</v>
       </c>
+      <c r="P256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13037,6 +13297,7 @@
       <c r="O257" t="n">
         <v>45</v>
       </c>
+      <c r="P257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13086,6 +13347,7 @@
       <c r="O258" t="n">
         <v>45</v>
       </c>
+      <c r="P258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13135,6 +13397,7 @@
       <c r="O259" t="n">
         <v>50</v>
       </c>
+      <c r="P259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13184,6 +13447,7 @@
       <c r="O260" t="n">
         <v>55</v>
       </c>
+      <c r="P260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13233,6 +13497,7 @@
       <c r="O261" t="n">
         <v>55</v>
       </c>
+      <c r="P261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13282,6 +13547,7 @@
       <c r="O262" t="n">
         <v>55</v>
       </c>
+      <c r="P262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13331,6 +13597,7 @@
       <c r="O263" t="n">
         <v>50</v>
       </c>
+      <c r="P263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13380,6 +13647,7 @@
       <c r="O264" t="n">
         <v>50</v>
       </c>
+      <c r="P264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13429,6 +13697,7 @@
       <c r="O265" t="n">
         <v>45</v>
       </c>
+      <c r="P265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13478,6 +13747,7 @@
       <c r="O266" t="n">
         <v>35</v>
       </c>
+      <c r="P266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13527,6 +13797,7 @@
       <c r="O267" t="n">
         <v>40</v>
       </c>
+      <c r="P267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13576,6 +13847,7 @@
       <c r="O268" t="n">
         <v>45</v>
       </c>
+      <c r="P268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13625,6 +13897,7 @@
       <c r="O269" t="n">
         <v>45</v>
       </c>
+      <c r="P269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13674,6 +13947,7 @@
       <c r="O270" t="n">
         <v>50</v>
       </c>
+      <c r="P270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13723,6 +13997,7 @@
       <c r="O271" t="n">
         <v>55</v>
       </c>
+      <c r="P271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13772,6 +14047,7 @@
       <c r="O272" t="n">
         <v>55</v>
       </c>
+      <c r="P272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13821,6 +14097,7 @@
       <c r="O273" t="n">
         <v>55</v>
       </c>
+      <c r="P273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13870,6 +14147,7 @@
       <c r="O274" t="n">
         <v>50</v>
       </c>
+      <c r="P274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13919,6 +14197,7 @@
       <c r="O275" t="n">
         <v>50</v>
       </c>
+      <c r="P275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13968,6 +14247,7 @@
       <c r="O276" t="n">
         <v>45</v>
       </c>
+      <c r="P276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14017,6 +14297,7 @@
       <c r="O277" t="n">
         <v>35</v>
       </c>
+      <c r="P277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14066,6 +14347,7 @@
       <c r="O278" t="n">
         <v>40</v>
       </c>
+      <c r="P278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14115,6 +14397,7 @@
       <c r="O279" t="n">
         <v>45</v>
       </c>
+      <c r="P279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14164,6 +14447,7 @@
       <c r="O280" t="n">
         <v>45</v>
       </c>
+      <c r="P280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14213,6 +14497,7 @@
       <c r="O281" t="n">
         <v>50</v>
       </c>
+      <c r="P281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14262,6 +14547,7 @@
       <c r="O282" t="n">
         <v>55</v>
       </c>
+      <c r="P282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14311,6 +14597,7 @@
       <c r="O283" t="n">
         <v>55</v>
       </c>
+      <c r="P283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14360,6 +14647,7 @@
       <c r="O284" t="n">
         <v>55</v>
       </c>
+      <c r="P284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14409,6 +14697,7 @@
       <c r="O285" t="n">
         <v>50</v>
       </c>
+      <c r="P285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14458,6 +14747,7 @@
       <c r="O286" t="n">
         <v>50</v>
       </c>
+      <c r="P286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14507,6 +14797,7 @@
       <c r="O287" t="n">
         <v>45</v>
       </c>
+      <c r="P287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14556,6 +14847,7 @@
       <c r="O288" t="n">
         <v>35</v>
       </c>
+      <c r="P288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14605,6 +14897,7 @@
       <c r="O289" t="n">
         <v>40</v>
       </c>
+      <c r="P289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14654,6 +14947,7 @@
       <c r="O290" t="n">
         <v>45</v>
       </c>
+      <c r="P290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14703,6 +14997,7 @@
       <c r="O291" t="n">
         <v>45</v>
       </c>
+      <c r="P291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14752,6 +15047,7 @@
       <c r="O292" t="n">
         <v>50</v>
       </c>
+      <c r="P292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14801,6 +15097,7 @@
       <c r="O293" t="n">
         <v>55</v>
       </c>
+      <c r="P293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -14850,6 +15147,7 @@
       <c r="O294" t="n">
         <v>55</v>
       </c>
+      <c r="P294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14899,6 +15197,7 @@
       <c r="O295" t="n">
         <v>55</v>
       </c>
+      <c r="P295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14948,6 +15247,7 @@
       <c r="O296" t="n">
         <v>50</v>
       </c>
+      <c r="P296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -14997,6 +15297,7 @@
       <c r="O297" t="n">
         <v>50</v>
       </c>
+      <c r="P297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15046,6 +15347,7 @@
       <c r="O298" t="n">
         <v>45</v>
       </c>
+      <c r="P298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15095,6 +15397,7 @@
       <c r="O299" t="n">
         <v>35</v>
       </c>
+      <c r="P299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15144,6 +15447,7 @@
       <c r="O300" t="n">
         <v>40</v>
       </c>
+      <c r="P300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15193,6 +15497,7 @@
       <c r="O301" t="n">
         <v>45</v>
       </c>
+      <c r="P301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15242,6 +15547,7 @@
       <c r="O302" t="n">
         <v>45</v>
       </c>
+      <c r="P302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15291,6 +15597,7 @@
       <c r="O303" t="n">
         <v>50</v>
       </c>
+      <c r="P303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15340,6 +15647,7 @@
       <c r="O304" t="n">
         <v>55</v>
       </c>
+      <c r="P304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15389,6 +15697,7 @@
       <c r="O305" t="n">
         <v>55</v>
       </c>
+      <c r="P305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15438,6 +15747,7 @@
       <c r="O306" t="n">
         <v>55</v>
       </c>
+      <c r="P306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15487,6 +15797,7 @@
       <c r="O307" t="n">
         <v>50</v>
       </c>
+      <c r="P307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15536,6 +15847,7 @@
       <c r="O308" t="n">
         <v>50</v>
       </c>
+      <c r="P308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15585,6 +15897,7 @@
       <c r="O309" t="n">
         <v>45</v>
       </c>
+      <c r="P309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15634,6 +15947,7 @@
       <c r="O310" t="n">
         <v>35</v>
       </c>
+      <c r="P310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15683,6 +15997,7 @@
       <c r="O311" t="n">
         <v>40</v>
       </c>
+      <c r="P311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15732,6 +16047,7 @@
       <c r="O312" t="n">
         <v>45</v>
       </c>
+      <c r="P312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15781,6 +16097,7 @@
       <c r="O313" t="n">
         <v>45</v>
       </c>
+      <c r="P313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15830,6 +16147,7 @@
       <c r="O314" t="n">
         <v>50</v>
       </c>
+      <c r="P314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -15879,6 +16197,7 @@
       <c r="O315" t="n">
         <v>55</v>
       </c>
+      <c r="P315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15928,6 +16247,7 @@
       <c r="O316" t="n">
         <v>55</v>
       </c>
+      <c r="P316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15977,6 +16297,7 @@
       <c r="O317" t="n">
         <v>55</v>
       </c>
+      <c r="P317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -16026,6 +16347,7 @@
       <c r="O318" t="n">
         <v>50</v>
       </c>
+      <c r="P318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -16075,6 +16397,7 @@
       <c r="O319" t="n">
         <v>50</v>
       </c>
+      <c r="P319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -16124,6 +16447,7 @@
       <c r="O320" t="n">
         <v>45</v>
       </c>
+      <c r="P320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -16173,6 +16497,7 @@
       <c r="O321" t="n">
         <v>35</v>
       </c>
+      <c r="P321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -16222,6 +16547,7 @@
       <c r="O322" t="n">
         <v>40</v>
       </c>
+      <c r="P322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -16271,6 +16597,7 @@
       <c r="O323" t="n">
         <v>45</v>
       </c>
+      <c r="P323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -16320,6 +16647,7 @@
       <c r="O324" t="n">
         <v>45</v>
       </c>
+      <c r="P324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -16369,6 +16697,7 @@
       <c r="O325" t="n">
         <v>50</v>
       </c>
+      <c r="P325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -16418,6 +16747,7 @@
       <c r="O326" t="n">
         <v>55</v>
       </c>
+      <c r="P326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -16467,6 +16797,7 @@
       <c r="O327" t="n">
         <v>55</v>
       </c>
+      <c r="P327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -16516,6 +16847,7 @@
       <c r="O328" t="n">
         <v>55</v>
       </c>
+      <c r="P328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -16565,6 +16897,7 @@
       <c r="O329" t="n">
         <v>50</v>
       </c>
+      <c r="P329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -16614,6 +16947,7 @@
       <c r="O330" t="n">
         <v>50</v>
       </c>
+      <c r="P330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -16663,6 +16997,7 @@
       <c r="O331" t="n">
         <v>45</v>
       </c>
+      <c r="P331" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
